--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -751,7 +751,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1079,10 +1079,8 @@
           <t>Pukal Rokka</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9861050515</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9861050515</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1172,10 +1170,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
@@ -1186,7 +1182,7 @@
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : no light in router  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -628,7 +628,30 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -643,10 +666,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -682,16 +705,29 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -739,8 +775,8 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="20" customWidth="1" min="32" max="32"/>
-    <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -751,10 +787,10 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="32" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="20" customWidth="1" min="50" max="50"/>
@@ -1216,6 +1252,210 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 8:30 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364527</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Vicky Shahi</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Vicky Shahi</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9841732382</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:30:04 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9801970444</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:28:36 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:30:04 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur Tikhedewal Chumlung Kirati Bhawan, , ,</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>bkeeshahi@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 1m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -787,7 +787,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1319,10 +1319,8 @@
           <t>Vicky Shahi</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9841732382</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9841732382</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1408,10 +1406,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1422,7 +1418,7 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -694,20 +694,20 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -741,7 +741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -754,10 +754,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -775,7 +775,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="27" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -787,7 +787,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1452,6 +1452,222 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 8:48 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359809</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Ashutosh Regmi</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Ashutosh Regmi</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9867171444</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:48:55 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9867171444</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 06:58:32 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:48:55 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.70175</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>27.655793801439316, 85.34194749764016, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>regmiashutosh3@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>03:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>CDB091A</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.3341</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>6d 13h 50m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -787,7 +787,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1519,10 +1519,8 @@
           <t>Ashutosh Regmi</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9867171444</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9867171444</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1557,10 +1555,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.70175</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.70175</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1616,25 +1612,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>CDB091A</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.3341</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.33410000000001</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -544,20 +544,38 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -616,19 +634,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -651,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -666,12 +684,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -687,6 +706,11 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -700,34 +724,59 @@
       <c r="B2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="3" t="n">
         <v>2</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="D3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C5" s="4" t="n">
         <v>3</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -741,23 +790,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX4"/>
+  <dimension ref="A1:AX7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -770,30 +819,30 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="27" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="28" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="28" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
-    <col width="20" customWidth="1" min="50" max="50"/>
+    <col width="23" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1660,6 +1709,642 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 9:28 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>no light issue in stb box</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364855</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Achhami</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Achhami</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9808426033</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 08:46:00 PM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>CHB9808426033</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:48:05 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:28:48 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>OM Shanti Chock - Palace Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>hellosachhami0@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>2d 12h 42m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>2d 15h 40m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 9:26 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366738</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Suman Puri</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Suman Puri</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9860372268</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 04:04:04 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9860372268</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 04:04:04 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:26:16 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.69367</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>"Near to Ananda Events &amp; Meetings Pvt.Ltd.,Shantinagar New Baneshwor Kathmandu Bagmati, Kathmandu 44</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>suman.puri2057@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L27-5</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.34479</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>17h 22m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>17h 22m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 9:18 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>upgrade to router</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366896</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Jonik Jung Thapa</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Jonik Jung Thapa</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9868731490</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:18:09 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9840418268</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 05:54:00 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:18:09 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.68117</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Koteshwor Mahadevsthan bridge, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>jishanjungthapa12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Bajgain</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.33836</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>15h 24m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -836,7 +836,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1776,10 +1776,8 @@
           <t>Sachit Achhami</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9808426033</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9808426033</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1851,10 +1849,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH5" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH5" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI5" s="3" t="inlineStr"/>
       <c r="AJ5" s="3" t="inlineStr"/>
@@ -1869,10 +1865,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
@@ -1883,7 +1877,7 @@
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1984,10 +1978,8 @@
           <t>Suman Puri</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9860372268</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9860372268</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2022,10 +2014,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.69367</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.69367</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -2077,25 +2067,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>L27-5</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.34479</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.34479</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -2186,20 +2172,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Jonik Jung Thapa</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9868731490</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9868731490</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2234,10 +2214,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.68117</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.68117</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -2293,25 +2271,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>3,5</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.33836</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.33835999999999</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade to router  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -634,19 +634,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX7"/>
+  <dimension ref="A1:AX8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -836,7 +836,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2319,6 +2319,222 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 9:56 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366738</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Suman Puri</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Suman Puri</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9860372268</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:56:03 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9860372268</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 04:04:04 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:56:03 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.69367</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>"Near to Ananda Events &amp; Meetings Pvt.Ltd.,Shantinagar New Baneshwor Kathmandu Bagmati, Kathmandu 44</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>suman.puri2057@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L27-5</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.34479</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>17h 51m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -546,36 +546,54 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>57.1%</t>
+      <c r="B5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -634,19 +652,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -669,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -684,13 +702,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -706,10 +725,15 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -725,9 +749,12 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="E2" s="6" t="n">
         <v>4</v>
       </c>
     </row>
@@ -741,42 +768,70 @@
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="E3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>6</v>
+      <c r="E6" s="4" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -790,11 +845,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX8"/>
+  <dimension ref="A1:AX9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -825,7 +880,7 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="30" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -2386,10 +2441,8 @@
           <t>Suman Puri</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9860372268</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9860372268</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2424,10 +2477,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.69367</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.69367</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2483,55 +2534,259 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L27-5</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.34479</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.34479</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>17h 51m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS8" s="3" t="inlineStr">
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:15 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Router / Adapter Faulty</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366999</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Surya moktan</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Surya moktan</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9803523762</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:15:42 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9803523762</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:08:23 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:15:42 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Kritipur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>00:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>4,4</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>17h 51m</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>15h 7m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV8" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW8" s="3" t="inlineStr">
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX8" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -752,10 +752,10 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX9"/>
+  <dimension ref="A1:AX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -858,10 +858,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -2649,10 +2649,8 @@
           <t>Surya moktan</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9803523762</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9803523762</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2720,10 +2718,8 @@
           <t>Router Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="AH9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH9" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
@@ -2742,10 +2738,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2756,37 +2750,253 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>15h 7m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
           <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS9" s="3" t="inlineStr">
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:25 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366755</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Godhuli Enterprise</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Godhuli Enterprise</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9851064611</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:25:26 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9801822380</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 04:23:45 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:25:26 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.68092</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Koteshwor, Mahadevsthan, suryadarshan tole, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>godhulienter@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>00:25 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Sameer Thapa</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>1,8</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.33994</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>15h 7m</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>18h 1m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV9" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router / Adapter Faulty   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW9" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AX9" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -564,36 +564,54 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
+      <c r="B6" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -608,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -664,30 +682,53 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>30.0%</t>
         </is>
       </c>
     </row>
@@ -702,14 +743,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -730,10 +772,15 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -752,9 +799,12 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="6" t="n">
         <v>5</v>
       </c>
     </row>
@@ -771,67 +821,101 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>8</v>
+      <c r="F7" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -845,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX10"/>
+  <dimension ref="A1:AX11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2851,10 +2935,8 @@
           <t>Godhuli Enterprise</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9851064611</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9851064611</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2889,10 +2971,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.68092</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.68092</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2948,55 +3028,259 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>1,8</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.33994</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.33994</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>18h 1m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS10" s="3" t="inlineStr">
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:20 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366652</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>karma gurung</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>karma gurung</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9841238889</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:20:22 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>CHB9841238889</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 02:46:35 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:20:22 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Buddha , Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>abcde@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>00:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Salbin Ghale</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L47-8</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT10" s="3" t="inlineStr">
-        <is>
-          <t>18h 1m</t>
-        </is>
-      </c>
-      <c r="AU10" s="3" t="inlineStr">
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>19h 33m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV10" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW10" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX10" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
     </row>
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -796,16 +796,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -906,16 +906,16 @@
         <v>3</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX11"/>
+  <dimension ref="A1:AX13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3143,10 +3143,8 @@
           <t>karma gurung</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9841238889</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9841238889</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3236,10 +3234,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
@@ -3250,35 +3246,467 @@
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>19h 33m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
           <t>Case : iptv issue  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS11" s="3" t="inlineStr">
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:59 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366558</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Rabindra Shrestha</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Rabindra Shrestha</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9860272522</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:59:25 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9860272522</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:34:59 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:59:25 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.6735</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Kumaripati Purnachandi Temple, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>rabindra_shr@hotmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>00:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L43A-1</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.31907</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT11" s="3" t="inlineStr">
-        <is>
-          <t>19h 33m</t>
-        </is>
-      </c>
-      <c r="AU11" s="3" t="inlineStr">
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>21h 24m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV11" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv issue  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW11" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
-        </is>
-      </c>
-      <c r="AX11" s="3" t="inlineStr">
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:01 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367161</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Yogesh Shrestha</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Yogesh Shrestha</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9802084488</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:01:30 AM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9802084488</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 08:53:31 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:01:30 AM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.73021</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>IOM International Organization for Migration Nepal - Non-profit organization Kathmandu 44600, Bagmat</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>yog354s@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>01:01 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>L62-2</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.331738</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>14h 7m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -582,36 +582,54 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>75.0%</t>
+      <c r="B7" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -670,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -705,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.1%</t>
         </is>
       </c>
     </row>
@@ -716,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
     </row>
@@ -743,15 +761,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -777,10 +796,15 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -802,10 +826,13 @@
         <v>1</v>
       </c>
       <c r="E2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="6" t="n">
-        <v>7</v>
+      <c r="G2" s="6" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -824,10 +851,13 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -848,7 +878,10 @@
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -870,7 +903,10 @@
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -892,7 +928,10 @@
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -912,10 +951,13 @@
         <v>2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -929,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX13"/>
+  <dimension ref="A1:AX15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3347,10 +3389,8 @@
           <t>Rabindra Shrestha</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9860272522</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9860272522</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3385,10 +3425,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.6735</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.6735</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -3444,25 +3482,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>L43A-1</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.31907</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.31907</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -3563,10 +3597,8 @@
           <t>Yogesh Shrestha</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9802084488</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9802084488</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3601,10 +3633,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.73021</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.73021</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3660,55 +3690,471 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>L62-2</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.331738</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.331738</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>14h 7m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS13" s="3" t="inlineStr">
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:09 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : setup box issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>setup box issue</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366814</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Pabitra khatri</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Pabitra khatri</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9865121028</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:09:44 AM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9865121028</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 05:12:53 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:09:44 AM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.655215</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Gamcha chowk near, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>01:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Abina Chitrakar</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>L46-2</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.393444</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : setup box issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT13" s="3" t="inlineStr">
-        <is>
-          <t>14h 7m</t>
-        </is>
-      </c>
-      <c r="AU13" s="3" t="inlineStr">
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>17h 56m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV13" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW13" s="3" t="inlineStr">
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : setup box issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:10 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6 upgardation   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>for wifi 6 upgardation</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366937</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Anita Bogati</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Anita Bogati</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9860370065</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:10:48 AM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>KLK9860673598</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 06:35:19 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:10:48 AM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Dallu Awasiya Vidhyalaya - Educational institution P852+V23 15 ??????? ????? Kathmandu 44600, Kathma</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>ms.anitabogati@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>01:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>CDB348</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6 upgardation   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>16h 35m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6 upgardation   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX13" s="3" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>11</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.7%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -888,17 +888,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -913,14 +913,14 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
@@ -936,28 +936,53 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="4" t="n">
+      <c r="D8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F8" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>13</v>
+      <c r="G8" s="4" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -971,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX15"/>
+  <dimension ref="A1:AX16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1017,7 +1042,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3805,10 +3830,8 @@
           <t>Pabitra khatri</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9865121028</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9865121028</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3843,10 +3866,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.655215</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.655215</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3898,25 +3919,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>L46-2</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.393444</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.393444</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : setup box issue  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -4017,10 +4034,8 @@
           <t>Anita Bogati</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9860370065</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9860370065</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -4110,10 +4125,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
@@ -4124,29 +4137,29 @@
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>16h 35m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
           <t>Case : for wifi 6 upgardation   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS15" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
-          <t>16h 35m</t>
-        </is>
-      </c>
-      <c r="AU15" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV15" s="3" t="inlineStr">
-        <is>
-          <t>Case : for wifi 6 upgardation   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="AW15" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -4155,6 +4168,114 @@
       <c r="AX15" s="3" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:24 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr"/>
+      <c r="V16" s="3" t="inlineStr"/>
+      <c r="W16" s="3" t="inlineStr"/>
+      <c r="X16" s="3" t="inlineStr"/>
+      <c r="Y16" s="3" t="inlineStr"/>
+      <c r="Z16" s="3" t="inlineStr"/>
+      <c r="AA16" s="3" t="inlineStr"/>
+      <c r="AB16" s="3" t="inlineStr"/>
+      <c r="AC16" s="3" t="inlineStr"/>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr"/>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr"/>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr"/>
+      <c r="AM16" s="3" t="inlineStr"/>
+      <c r="AN16" s="3" t="inlineStr"/>
+      <c r="AO16" s="3" t="inlineStr"/>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>72.2%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -734,14 +734,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -882,48 +882,48 @@
         <v>0</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -973,16 +973,16 @@
         <v>2</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>5</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -996,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX16"/>
+  <dimension ref="A1:AX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1042,7 +1042,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4279,6 +4279,626 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:28 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Router faulty</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367285</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Menuka adhikari</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Menuka adhikari</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9829343940</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:28:58 AM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9829343940</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 07:47:07 AM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:28:58 AM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Chamati, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr"/>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>01:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>1,6</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>3h 41m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:46 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367040</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Deepak Babu Bhatta</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Deepak Babu Bhatta</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9860985865</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 09:44:48 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>KLK9860985865</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:30:34 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:46:45 AM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Radha Krishna Temple, Raniban - Hindu temple P7JP+2X5 Radha Krishna Chowk, Yerahity Raniban Rd Nagar</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>9860985865@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>CDB647</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>14h 1m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>16h 16m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:38 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364527</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Vicky Shahi</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Vicky Shahi</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9841732382</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:38:26 AM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9801970444</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:28:36 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:38:26 AM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur Tikhedewal Chumlung Kirati Bhawan, , ,</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>bkeeshahi@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>18:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 9m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -688,14 +688,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.0%</t>
         </is>
       </c>
     </row>
@@ -829,10 +829,10 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -979,10 +979,10 @@
         <v>2</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -996,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX19"/>
+  <dimension ref="A1:AX21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4346,10 +4346,8 @@
           <t>Menuka adhikari</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9829343940</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9829343940</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4435,10 +4433,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
@@ -4449,7 +4445,7 @@
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -4550,10 +4546,8 @@
           <t>Deepak Babu Bhatta</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9860985865</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9860985865</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4625,10 +4619,8 @@
           <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="AH18" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH18" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI18" s="3" t="inlineStr"/>
       <c r="AJ18" s="3" t="inlineStr"/>
@@ -4643,10 +4635,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
@@ -4657,7 +4647,7 @@
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4758,10 +4748,8 @@
           <t>Vicky Shahi</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9841732382</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9841732382</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4851,10 +4839,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
@@ -4865,37 +4851,461 @@
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 9m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
           <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS19" s="3" t="inlineStr">
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:56 AM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367391</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Priyasha Shah</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Priyasha Shah</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9861494544</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:09:03 AM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9861494544</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:09:03 AM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:56:37 AM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.67509</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Koteshwor Bhatbhateni - Opposite By Cosmic International Academy, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>priyashashah37@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.34637</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>2h 47m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>2h 47m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:51 AM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>no light issue in stb box</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364855</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Achhami</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Achhami</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9808426033</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:51:04 AM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>CHB9808426033</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:48:05 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:51:04 AM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>OM Shanti Chock - Palace Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>hellosachhami0@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>14:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>2d 22h 9m</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>2d 18h 2m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV19" s="3" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW19" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX19" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>40.9%</t>
         </is>
       </c>
     </row>
@@ -823,16 +823,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -973,16 +973,16 @@
         <v>2</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>6</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -996,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX21"/>
+  <dimension ref="A1:AX23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1009,10 +1009,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -1030,7 +1030,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="32" customWidth="1" min="32" max="32"/>
     <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -4952,10 +4952,8 @@
           <t>Priyasha Shah</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9861494544</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9861494544</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4990,10 +4988,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>27.67509</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>27.67509</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -5045,25 +5041,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>2,4</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.34637</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.34636999999999</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -5164,10 +5156,8 @@
           <t>Sachit Achhami</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9808426033</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9808426033</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -5239,10 +5229,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH21" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH21" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI21" s="3" t="inlineStr">
         <is>
@@ -5261,10 +5249,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
@@ -5275,37 +5261,469 @@
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>2d 18h 2m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
           <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS21" s="3" t="inlineStr">
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:10 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366549</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Janak Adhikari</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Janak Adhikari</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9860577686</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:10:17 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9841728074</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 01:28:33 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:10:17 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.73023</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Tushal Multivenue - Event venue Tushal 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>adhikarihrithik2022@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>02:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>L55-4</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.3151</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT21" s="3" t="inlineStr">
-        <is>
-          <t>2d 18h 2m</t>
-        </is>
-      </c>
-      <c r="AU21" s="3" t="inlineStr">
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>22h 41m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV21" s="3" t="inlineStr">
-        <is>
-          <t>Case : no light issue in stb box  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW21" s="3" t="inlineStr">
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:04 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367312</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Tilak bahadur bohora</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Tilak bahadur bohora</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9841279916</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX21" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:04:04 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9841279916</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:28:49 AM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:04:04 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.735677</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Sweet Heart Montessori &amp; Day Care Bohoratar road, ???????? 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>anjilabohora76@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>02:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.295385</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>3h 35m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -1042,7 +1042,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -5362,10 +5362,8 @@
           <t>Janak Adhikari</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9860577686</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9860577686</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -5400,10 +5398,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.73023</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.73023</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -5459,25 +5455,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>L55-4</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.3151</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.3151</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -5578,10 +5570,8 @@
           <t>Tilak bahadur bohora</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9841279916</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9841279916</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -5616,10 +5606,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>27.735677</t>
-        </is>
+      <c r="Y23" s="3" t="n">
+        <v>27.735677</v>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
@@ -5675,25 +5663,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>3,1</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.295385</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.295385</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>73.9%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>43.5%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.7%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>43.5%</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>2</v>
@@ -832,7 +832,7 @@
         <v>4</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -970,7 +970,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>5</v>
@@ -982,7 +982,7 @@
         <v>6</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -996,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX23"/>
+  <dimension ref="A1:AX24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1042,7 +1042,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -5711,6 +5711,222 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:41 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367602</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Roji Shrestha</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Roji Shrestha</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9840050285</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:41:01 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9840050285</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 10:53:33 AM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:41:01 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.67496</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>near Panga Dobato Bus Stop Panga Rd, Kirtipur , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>ara.readymade@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>01:48 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>CDB141</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.28072</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>1h 47m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -616,20 +616,38 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>73.9%</t>
+      <c r="B8" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -688,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
     </row>
@@ -723,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
     </row>
@@ -734,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -761,16 +779,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -806,6 +825,11 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -831,14 +855,17 @@
       <c r="F2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G2" s="6" t="n">
-        <v>12</v>
+      <c r="G2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -848,22 +875,25 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -873,15 +903,18 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -906,14 +939,17 @@
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -923,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -931,24 +967,27 @@
       <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -956,33 +995,67 @@
       <c r="F7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F9" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>20</v>
+      <c r="G9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -996,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX24"/>
+  <dimension ref="A1:AX29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1009,10 +1082,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -1031,7 +1104,7 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="32" customWidth="1" min="32" max="32"/>
-    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -5778,10 +5851,8 @@
           <t>Roji Shrestha</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9840050285</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9840050285</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5816,10 +5887,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.67496</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.67496</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -5875,47 +5944,43 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>CDB141</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.28072</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.28072</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>1h 47m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS24" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT24" s="3" t="inlineStr">
-        <is>
-          <t>1h 47m</t>
-        </is>
-      </c>
-      <c r="AU24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV24" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="AW24" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -5924,6 +5989,1038 @@
       <c r="AX24" s="3" t="inlineStr">
         <is>
           <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:57 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>stb adapter damage issue</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366894</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Shivaraj Ojhaya  Tharu</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Shivaraj Ojhaya  Tharu</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9848949572</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 06:10:46 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>KLK9848949572</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 05:52:33 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:57:32 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Khadka Gaun 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>9811155449@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>02:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Bhumika Saud</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>2,12</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr"/>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>18h 46m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>19h 4m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:56 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>stb adapter damage issue</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366894</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Shivaraj Ojhaya  Tharu</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Shivaraj Ojhaya  Tharu</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9848949572</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 06:10:46 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>KLK9848949572</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 05:52:33 PM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:57:32 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr"/>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Khadka Gaun 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr">
+        <is>
+          <t>9811155449@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>02:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Bhumika Saud</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>2,12</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr"/>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>18h 46m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>19h 4m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX26" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:54 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366465</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Adhikari</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Adhikari</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9840779767</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:38:47 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>KLK9840779767</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 12:38:47 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:54:48 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>27.696517, 85.289584 - Makalu Oil Store, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>sunitarijal45@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>02:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>CDB318</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr"/>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>1d 16m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>1d 16m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:53 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365507</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Uttam Kumar Poudel</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Uttam Kumar Poudel</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9824866858</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:01:14 PM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>9824866858</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:01:14 PM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:53:02 PM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>27.690688, 85.250552, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr"/>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>09:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>CDB594</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 51m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 51m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:52 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365507</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Uttam Kumar Poudel</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Uttam Kumar Poudel</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9824866858</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:01:14 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9824866858</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:01:14 PM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:53:02 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>27.690688, 85.250552, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr"/>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>09:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>CDB594</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 51m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 51m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX29" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>79.3%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>44.8%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>10.3%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>41.4%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -865,7 +865,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -875,13 +875,13 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -893,23 +893,23 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -921,20 +921,20 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>NETTV-STB App not working</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -962,13 +962,13 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>1</v>
@@ -977,7 +977,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -996,7 +996,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>1</v>
@@ -1005,17 +1005,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
@@ -1031,31 +1031,59 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>23</v>
+      <c r="H10" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1069,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX29"/>
+  <dimension ref="A1:AX30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6059,10 +6087,8 @@
           <t>Shivaraj Ojhaya  Tharu</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9848949572</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9848949572</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -6152,10 +6178,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
@@ -6166,7 +6190,7 @@
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -6267,10 +6291,8 @@
           <t>Shivaraj Ojhaya  Tharu</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9848949572</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9848949572</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -6360,10 +6382,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
@@ -6374,7 +6394,7 @@
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : stb adapter damage issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -6475,10 +6495,8 @@
           <t>Sunita Adhikari</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9840779767</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9840779767</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -6568,10 +6586,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
@@ -6582,7 +6598,7 @@
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -6683,10 +6699,8 @@
           <t>Uttam Kumar Poudel</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9824866858</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9824866858</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -6772,10 +6786,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
@@ -6786,7 +6798,7 @@
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
@@ -6887,10 +6899,8 @@
           <t>Uttam Kumar Poudel</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9824866858</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9824866858</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6976,10 +6986,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
@@ -6990,29 +6998,29 @@
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 51m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 51m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS29" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 51m</t>
-        </is>
-      </c>
-      <c r="AT29" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 51m</t>
-        </is>
-      </c>
-      <c r="AU29" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV29" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -7021,6 +7029,222 @@
       <c r="AX29" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 1:05 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>NETTV issue</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367427</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Ghanashyam Adhikari</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Ghanashyam Adhikari</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9851043225</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:05:03 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>CHB9851043225</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:22:32 AM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:05:03 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>27.769556032831318, 85.35235214866094, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>9851043225@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-STB App not working</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>03:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>3h 42m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7099,10 +7099,8 @@
           <t>Ghanashyam Adhikari</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9851043225</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9851043225</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -7137,10 +7135,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y30" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y30" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
@@ -7196,25 +7192,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
           <t>1,16</t>
         </is>
       </c>
-      <c r="AP30" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP30" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : NETTV issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>43.3%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>43.3%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
         <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>4</v>
@@ -859,7 +859,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -1074,7 +1074,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>6</v>
@@ -1083,7 +1083,7 @@
         <v>3</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX30"/>
+  <dimension ref="A1:AX31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7240,6 +7240,226 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 1:38 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367645</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Mandip Shigh</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Mandip Shigh</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9851064551</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:38:57 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9851064551</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 11:15:50 AM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:38:57 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>27.73937</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Digital Cube Store Details from Google Maps Ganeshthan, Kathmandu 44600 +977 980-8123241  , Bagmati,</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>mandipchauhan2012@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>02:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>85.31483</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>2h 23m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7307,10 +7307,8 @@
           <t>Mandip Shigh</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9851064551</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9851064551</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -7345,10 +7343,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>27.73937</t>
-        </is>
+      <c r="Y31" s="3" t="n">
+        <v>27.73937</v>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
@@ -7386,10 +7382,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH31" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH31" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
@@ -7408,25 +7402,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>85.31483</t>
-        </is>
+      <c r="AP31" s="3" t="n">
+        <v>85.31483</v>
       </c>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.4%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
     </row>
@@ -856,10 +856,10 @@
         <v>4</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -884,10 +884,10 @@
         <v>2</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1080,10 +1080,10 @@
         <v>6</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX31"/>
+  <dimension ref="A1:AX33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1110,10 +1110,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="43" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="43" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7450,6 +7450,438 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 2:17 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367298</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Finovate Advisory &amp; Consulting Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Finovate Advisory &amp; Consulting Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9840450592</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:07:10 AM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9840450592</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:07:10 AM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:17:11 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.69576</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>M7WG+JRW, Nagarjun,Near by Welcome meat mart, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>nischalpathak62@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>04:17 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.27662</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>6h 10m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>6h 10m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 2:15 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : replace skycom to nettv   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>replace skycom to nettv</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367473</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Lamsal</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Lamsal</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9840527775</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:40:20 AM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9851328488</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 09:40:20 AM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:15:22 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>27.699563</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Syuchatar, Kathmandu 44600 near by Syuchatar Pati Chowk ????????? ???? ???, , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>lamsalsaurav555@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>04:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>85.274141</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : replace skycom to nettv   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>4h 35m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>4h 35m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : replace skycom to nettv   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7517,10 +7517,8 @@
           <t>Finovate Advisory &amp; Consulting Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9840450592</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9840450592</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -7555,10 +7553,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.69576</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.69576</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -7614,25 +7610,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.27662</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.27661999999999</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
@@ -7733,10 +7725,8 @@
           <t>Saurav Lamsal</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9840527775</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9840527775</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -7771,10 +7761,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>27.699563</t>
-        </is>
+      <c r="Y33" s="3" t="n">
+        <v>27.699563</v>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
@@ -7830,25 +7818,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>85.274141</t>
-        </is>
+      <c r="AP33" s="3" t="n">
+        <v>85.274141</v>
       </c>
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : replace skycom to nettv   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>82.4%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>44.1%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>44.1%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>2</v>
@@ -859,7 +859,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -949,11 +949,11 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>NETTV-STB App not working</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -962,16 +962,16 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1005,7 +1005,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>NETTV-STB App not working</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -1033,17 +1033,17 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
@@ -1068,7 +1068,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>5</v>
@@ -1077,13 +1077,13 @@
         <v>5</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>5</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX33"/>
+  <dimension ref="A1:AX35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1110,10 +1110,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="43" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="43" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7866,6 +7866,438 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 2:29 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366682</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Ram Sita Bahuudyassa Sahakari Sasta Limited</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Ram Sita Bahuudyassa Sahakari Sasta Limited</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9843174089</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:29:19 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9808235412</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 03:03:53 PM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:29:19 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>27.68546</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Near Everest Momo Center, Kuleshor , Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>anilsinghkr73@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>04:29 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>85.29819</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>23h 25m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 2:27 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN ROUTER  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>NO LIGHT IN ROUTER</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367789</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Anjali Shrestha</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Anjali Shrestha</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9841132622</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:27:24 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>BKT9841132622</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:40:06 PM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:27:24 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Radheradhe, Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>1@g.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>01:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>L52-6</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN ROUTER  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>1h 47m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN ROUTER  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7933,10 +7933,8 @@
           <t>Ram Sita Bahuudyassa Sahakari Sasta Limited</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9843174089</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9843174089</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -7971,10 +7969,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>27.68546</t>
-        </is>
+      <c r="Y34" s="3" t="n">
+        <v>27.68546</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -8030,25 +8026,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>3,5</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>85.29819</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>85.29819000000001</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
@@ -8149,10 +8141,8 @@
           <t>Anjali Shrestha</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9841132622</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9841132622</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -8187,10 +8177,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
@@ -8246,25 +8234,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>L52-6</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : NO LIGHT IN ROUTER  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>28</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX35"/>
+  <dimension ref="A1:AX36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8282,6 +8282,114 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 3:11 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr"/>
+      <c r="L36" s="3" t="inlineStr"/>
+      <c r="M36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="inlineStr"/>
+      <c r="O36" s="3" t="inlineStr"/>
+      <c r="P36" s="3" t="inlineStr"/>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr"/>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr"/>
+      <c r="V36" s="3" t="inlineStr"/>
+      <c r="W36" s="3" t="inlineStr"/>
+      <c r="X36" s="3" t="inlineStr"/>
+      <c r="Y36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="inlineStr"/>
+      <c r="AA36" s="3" t="inlineStr"/>
+      <c r="AB36" s="3" t="inlineStr"/>
+      <c r="AC36" s="3" t="inlineStr"/>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr"/>
+      <c r="AF36" s="3" t="inlineStr"/>
+      <c r="AG36" s="3" t="inlineStr"/>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr"/>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr"/>
+      <c r="AM36" s="3" t="inlineStr"/>
+      <c r="AN36" s="3" t="inlineStr"/>
+      <c r="AO36" s="3" t="inlineStr"/>
+      <c r="AP36" s="3" t="inlineStr"/>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX36" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>80.6%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -853,13 +853,13 @@
         <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -1077,13 +1077,13 @@
         <v>5</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>5</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX36"/>
+  <dimension ref="A1:AX37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -8390,6 +8390,210 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 3:11 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367703</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Jamuna Gurung</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Jamuna Gurung</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9843654354</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:11:20 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9843654354</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 12:01:36 PM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:11:20 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr"/>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Near comedy height, baneshwor, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr"/>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>03:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>4,5</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr"/>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>3h 9m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -8457,10 +8457,8 @@
           <t>Jamuna Gurung</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9843654354</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9843654354</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -8546,10 +8544,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
@@ -8560,7 +8556,7 @@
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>81.1%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>43.2%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.1%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.2%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>2</v>
@@ -859,7 +859,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -1068,7 +1068,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>5</v>
@@ -1083,7 +1083,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX37"/>
+  <dimension ref="A1:AX38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -8590,6 +8590,226 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 4:10 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367847</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Pawan Ghimire</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Pawan Ghimire</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9761325251</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 04:10:12 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>9851053640</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:22:36 PM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 04:10:12 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>27.70455</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>National Trauma Center new read , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>02:48 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>CDB216</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>85.31256</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>2h 47m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -8657,10 +8657,8 @@
           <t>Pawan Ghimire</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9761325251</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9761325251</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -8695,10 +8693,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>27.70455</t>
-        </is>
+      <c r="Y38" s="3" t="n">
+        <v>27.70455</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
@@ -8736,10 +8732,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH38" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH38" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
@@ -8758,25 +8752,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>CDB216</t>
         </is>
       </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>85.31256</t>
-        </is>
+      <c r="AP38" s="3" t="n">
+        <v>85.31256</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>81.6%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>44.7%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>7.9%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>42.1%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>2</v>
@@ -859,7 +859,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -1068,7 +1068,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>5</v>
@@ -1083,7 +1083,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX38"/>
+  <dimension ref="A1:AX39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -8800,6 +8800,222 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 5:26 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1368012</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Akhileshwar Singh</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Akhileshwar Singh</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9841374223</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 05:26:52 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>9841374223</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:31:26 PM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 05:26:52 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t>27.6676</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>Damodar Marga, Lalitpur,Green Tara International Overseas (P) Ltd., Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>aksileshwar.singh12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>01:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>2,12</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>85.3133</t>
+        </is>
+      </c>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>1h 55m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -8867,10 +8867,8 @@
           <t>Akhileshwar Singh</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9841374223</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9841374223</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -8905,10 +8903,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t>27.6676</t>
-        </is>
+      <c r="Y39" s="3" t="n">
+        <v>27.6676</v>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
@@ -8964,25 +8960,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
           <t>2,12</t>
         </is>
       </c>
-      <c r="AP39" s="3" t="inlineStr">
-        <is>
-          <t>85.3133</t>
-        </is>
+      <c r="AP39" s="3" t="n">
+        <v>85.3133</v>
       </c>
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>82.1%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>7.7%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>41.0%</t>
         </is>
       </c>
     </row>
@@ -893,29 +893,29 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -949,23 +949,23 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -1071,7 +1071,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>5</v>
@@ -1083,7 +1083,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX39"/>
+  <dimension ref="A1:AX40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -9008,6 +9008,198 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 8:30 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : ONT Replacement  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>ONT Replacement</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1368015</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Height Restro and wellness</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Height Restro and wellness</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9843760166</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:30:25 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>LS632</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:34:16 PM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 08:30:25 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr"/>
+      <c r="Y40" s="3" t="inlineStr"/>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Salesberry building Maharajgunj , , ,</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr"/>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>04:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Ghising</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr"/>
+      <c r="AO40" s="3" t="inlineStr"/>
+      <c r="AP40" s="3" t="inlineStr"/>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : ONT Replacement  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>4h 56m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : ONT Replacement  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX40" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_12_Oct_2026.xlsx
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -9065,20 +9065,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M40" s="3" t="inlineStr"/>
       <c r="N40" s="3" t="inlineStr">
         <is>
           <t>Height Restro and wellness</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9843760166</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9843760166</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -9166,7 +9160,7 @@
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>Case : ONT Replacement  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
